--- a/demo/asteria/sources/governance/approved_audit_plan_2026.xlsx
+++ b/demo/asteria/sources/governance/approved_audit_plan_2026.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
-    <sheet name="Capacity" sheetId="2" r:id="rId2"/>
+    <sheet name="Excluded" sheetId="2" r:id="rId2"/>
+    <sheet name="Capacity" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -283,6 +284,411 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AST-SLA-2026-H2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer service commitments</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AST-R-SLA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AST-VULN-2026-H1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Vulnerability and patch management</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AST-R-VULN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AST-LOG-2026-H1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Logging and monitoring</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AST-R-LOG</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AST-KEY-2026-H2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Key management</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AST-R-KEY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AST-BCP-2026-H1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Business continuity and backup</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AST-R-BACKUP</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AST-SEG-2026-H2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Segregation of duties</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AST-R-SEG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AST-VEN-2026-H2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Third-party and subprocessor management</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AST-R-VENDOR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AST-HR-2026-H1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Joiner, mover, leaver — people process</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AST-R-PAYROLL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AST-AI-2026-H2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Governance of automated decisioning</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AST-R-AI</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -293,44 +699,240 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>resource</t>
+          <t>risk_ref</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>available_days</t>
+          <t>risk</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>allocated_days</t>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>reason_not_covered</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>residual_accepted_by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Co-sourced assurance provider</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>60</v>
-      </c>
-      <c r="C2">
-        <v>51</v>
+          <t>AST-R-CONC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Revenue concentration in a single customer</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Board-level strategic risk; monitored by the Board directly rather than through assurance</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>board</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>AST-R-AML</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Counterparty screening fails to identify a sanctioned party</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Covered by the external compliance review commissioned in Q1 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AST-R-TAX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Indirect tax is misdeclared across jurisdictions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Covered by the statutory auditor's tax procedures</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AST-R-PHYS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Unauthorised physical access to the Paris office</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rating below the coverage threshold agreed for 2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AST-R-KEYPERSON</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Loss of a single engineer with undocumented knowledge</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No plannable capacity remains in 2026; carried to the 2027 plan</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AST-R-SDLC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Defect reaches production through inadequate testing</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Partially covered within AST-SCM-2026-H2; no standalone engagement</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>audit-committee</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>resource</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>available_days</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>allocated_days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Co-sourced assurance provider</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>96</v>
+      </c>
+      <c r="C2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Internal control owner support</t>
         </is>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
